--- a/healthcare_forms/040_patient_portal_consent_form--healthcare_forms.xlsx
+++ b/healthcare_forms/040_patient_portal_consent_form--healthcare_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -671,12 +671,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'id':_1,_'name':_'consent_to_share_information_with_healthcare_provider',_'label':_'consent_to_share_information_with_healthcare_provider'}</t>
+          <t>consent_to_share_information_with_healthcare_provider</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'id': 1, 'name': 'consent_to_share_information_with_healthcare_provider', 'label': 'Consent to share information with healthcare provider'}</t>
+          <t>Consent to share information with healthcare provider</t>
         </is>
       </c>
     </row>
@@ -688,12 +688,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'id':_2,_'name':_'consent_to_share_information_with_insurance_company',_'label':_'consent_to_share_information_with_insurance_company'}</t>
+          <t>consent_to_share_information_with_insurance_company</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'id': 2, 'name': 'consent_to_share_information_with_insurance_company', 'label': 'Consent to share information with insurance company'}</t>
+          <t>Consent to share information with insurance company</t>
         </is>
       </c>
     </row>
@@ -705,12 +705,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'id':_3,_'name':_'consent_to_share_information_with_family_member',_'label':_'consent_to_share_information_with_family_member'}</t>
+          <t>consent_to_share_information_with_family_member</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'id': 3, 'name': 'consent_to_share_information_with_family_member', 'label': 'Consent to share information with family member'}</t>
+          <t>Consent to share information with family member</t>
         </is>
       </c>
     </row>
